--- a/grossdie.xlsx
+++ b/grossdie.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wenqiang.ding\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wenqiang.ding\Desktop\0401\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1CBA38E-230F-4815-A510-46A2354C1CAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9FD0AA5-8F87-4B64-8875-3C99ECF88BDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,10 +27,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="191">
   <si>
-    <t>品名</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>GROSS DIE</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -778,6 +774,10 @@
   </si>
   <si>
     <t>ZH6342A</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>晶圆</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1230,15 +1230,15 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B2" s="4">
         <v>11463</v>
@@ -1246,7 +1246,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B3" s="4">
         <v>11463</v>
@@ -1254,7 +1254,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B4" s="4">
         <v>11463</v>
@@ -1262,7 +1262,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B5" s="4">
         <v>11463</v>
@@ -1270,7 +1270,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6" s="4">
         <v>11463</v>
@@ -1278,7 +1278,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" s="4">
         <v>11463</v>
@@ -1286,7 +1286,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B8" s="4">
         <v>37000</v>
@@ -1294,7 +1294,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B9" s="4">
         <v>7700</v>
@@ -1302,7 +1302,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B10" s="4">
         <v>7700</v>
@@ -1310,7 +1310,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B11" s="4">
         <v>7700</v>
@@ -1318,7 +1318,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B12" s="4">
         <v>5665</v>
@@ -1326,7 +1326,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B13" s="4">
         <v>28507</v>
@@ -1334,7 +1334,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B14" s="4">
         <v>28507</v>
@@ -1342,7 +1342,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B15" s="4">
         <v>28507</v>
@@ -1350,7 +1350,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B16" s="4">
         <v>28507</v>
@@ -1358,7 +1358,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B17" s="4">
         <v>28507</v>
@@ -1366,7 +1366,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B18" s="4">
         <v>19900</v>
@@ -1374,7 +1374,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B19" s="4">
         <v>19900</v>
@@ -1382,7 +1382,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B20" s="4">
         <v>24053</v>
@@ -1390,7 +1390,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B21" s="4">
         <v>24053</v>
@@ -1398,7 +1398,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B22" s="4">
         <v>24053</v>
@@ -1406,7 +1406,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B23" s="4">
         <v>16204</v>
@@ -1414,7 +1414,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B24" s="4">
         <v>16204</v>
@@ -1422,7 +1422,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B25" s="4">
         <v>16204</v>
@@ -1430,7 +1430,7 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B26" s="4">
         <v>16204</v>
@@ -1438,7 +1438,7 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B27" s="4">
         <v>16204</v>
@@ -1446,7 +1446,7 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B28" s="4">
         <v>16204</v>
@@ -1454,7 +1454,7 @@
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B29" s="4">
         <v>16204</v>
@@ -1462,7 +1462,7 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B30" s="4">
         <v>16204</v>
@@ -1470,7 +1470,7 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B31" s="4">
         <v>16204</v>
@@ -1478,7 +1478,7 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B32" s="4">
         <v>9000</v>
@@ -1486,7 +1486,7 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B33" s="4">
         <v>7854</v>
@@ -1494,7 +1494,7 @@
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B34" s="4">
         <v>3233</v>
@@ -1502,7 +1502,7 @@
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B35" s="4">
         <v>3233</v>
@@ -1510,7 +1510,7 @@
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B36" s="4">
         <v>3233</v>
@@ -1518,7 +1518,7 @@
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A37" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B37" s="4">
         <v>4000</v>
@@ -1526,7 +1526,7 @@
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B38" s="4">
         <v>4000</v>
@@ -1534,7 +1534,7 @@
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A39" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B39" s="4">
         <v>13888</v>
@@ -1542,7 +1542,7 @@
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B40" s="4">
         <v>14500</v>
@@ -1550,7 +1550,7 @@
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A41" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B41" s="4">
         <v>24053</v>
@@ -1558,7 +1558,7 @@
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A42" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B42" s="4">
         <v>24053</v>
@@ -1566,7 +1566,7 @@
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A43" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B43" s="4">
         <v>4250</v>
@@ -1574,7 +1574,7 @@
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A44" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B44" s="4">
         <v>4250</v>
@@ -1582,7 +1582,7 @@
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A45" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B45" s="4">
         <v>6942</v>
@@ -1590,7 +1590,7 @@
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A46" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B46" s="4">
         <v>16204</v>
@@ -1598,7 +1598,7 @@
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A47" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B47" s="4">
         <v>16204</v>
@@ -1606,7 +1606,7 @@
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A48" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B48" s="4">
         <v>16204</v>
@@ -1614,7 +1614,7 @@
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A49" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B49" s="4">
         <v>3947</v>
@@ -1622,7 +1622,7 @@
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A50" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B50" s="4">
         <v>38147</v>
@@ -1630,7 +1630,7 @@
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A51" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B51" s="4">
         <v>38147</v>
@@ -1638,7 +1638,7 @@
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A52" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B52" s="4">
         <v>38147</v>
@@ -1646,7 +1646,7 @@
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A53" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B53" s="4">
         <v>38147</v>
@@ -1654,7 +1654,7 @@
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A54" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B54" s="4">
         <v>20915</v>
@@ -1662,7 +1662,7 @@
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A55" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B55" s="4">
         <v>20920</v>
@@ -1670,7 +1670,7 @@
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A56" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B56" s="4">
         <v>27000</v>
@@ -1678,7 +1678,7 @@
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A57" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B57" s="4">
         <v>16194</v>
@@ -1686,7 +1686,7 @@
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A58" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B58" s="4">
         <v>16194</v>
@@ -1694,7 +1694,7 @@
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A59" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B59" s="4">
         <v>16194</v>
@@ -1702,7 +1702,7 @@
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A60" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B60" s="4">
         <v>16194</v>
@@ -1710,7 +1710,7 @@
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A61" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B61" s="4">
         <v>16194</v>
@@ -1718,7 +1718,7 @@
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A62" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B62" s="4">
         <v>16194</v>
@@ -1726,7 +1726,7 @@
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A63" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B63" s="4">
         <v>20920</v>
@@ -1734,7 +1734,7 @@
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A64" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B64" s="4">
         <v>11249</v>
@@ -1742,7 +1742,7 @@
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A65" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B65" s="4">
         <v>11249</v>
@@ -1750,7 +1750,7 @@
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A66" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B66" s="4">
         <v>18810</v>
@@ -1758,7 +1758,7 @@
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A67" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B67" s="4">
         <v>28507</v>
@@ -1766,7 +1766,7 @@
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A68" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B68" s="4">
         <v>28507</v>
@@ -1774,7 +1774,7 @@
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A69" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B69" s="4">
         <v>28507</v>
@@ -1782,7 +1782,7 @@
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A70" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B70" s="4">
         <v>28507</v>
@@ -1790,7 +1790,7 @@
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A71" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B71" s="4">
         <v>28507</v>
@@ -1798,7 +1798,7 @@
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A72" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B72" s="4">
         <v>18326</v>
@@ -1806,7 +1806,7 @@
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A73" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B73" s="4">
         <v>15391</v>
@@ -1814,7 +1814,7 @@
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A74" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B74" s="4">
         <v>7368</v>
@@ -1822,7 +1822,7 @@
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A75" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B75" s="4">
         <v>8134</v>
@@ -1830,7 +1830,7 @@
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A76" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B76" s="4">
         <v>8134</v>
@@ -1838,7 +1838,7 @@
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A77" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B77" s="4">
         <v>8134</v>
@@ -1846,7 +1846,7 @@
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A78" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B78" s="4">
         <v>7090</v>
@@ -1854,7 +1854,7 @@
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A79" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B79" s="4">
         <v>7090</v>
@@ -1862,7 +1862,7 @@
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A80" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B80" s="4">
         <v>7368</v>
@@ -1870,7 +1870,7 @@
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A81" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B81" s="4">
         <v>3308</v>
@@ -1878,7 +1878,7 @@
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A82" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B82" s="4">
         <v>4278</v>
@@ -1886,7 +1886,7 @@
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A83" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B83" s="4">
         <v>1833</v>
@@ -1894,7 +1894,7 @@
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A84" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B84" s="4">
         <v>1833</v>
@@ -1902,7 +1902,7 @@
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A85" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B85" s="4">
         <v>6308</v>
@@ -1910,7 +1910,7 @@
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A86" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B86" s="4">
         <v>6100</v>
@@ -1918,7 +1918,7 @@
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A87" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B87" s="4">
         <v>28400</v>
@@ -1926,7 +1926,7 @@
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A88" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B88" s="4">
         <v>28400</v>
@@ -1934,7 +1934,7 @@
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A89" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B89" s="4">
         <v>2214</v>
@@ -1942,7 +1942,7 @@
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A90" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B90" s="4">
         <v>45000</v>
@@ -1950,7 +1950,7 @@
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A91" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B91" s="4">
         <v>43500</v>
@@ -1958,7 +1958,7 @@
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A92" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B92" s="4">
         <v>45000</v>
@@ -1966,7 +1966,7 @@
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A93" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B93" s="4">
         <v>45000</v>
@@ -1974,7 +1974,7 @@
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A94" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B94" s="4">
         <v>43548</v>
@@ -1982,7 +1982,7 @@
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A95" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B95" s="4">
         <v>26000</v>
@@ -1990,7 +1990,7 @@
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A96" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B96" s="4">
         <v>10000</v>
@@ -1998,7 +1998,7 @@
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A97" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B97" s="4">
         <v>27314</v>
@@ -2006,7 +2006,7 @@
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A98" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B98" s="4">
         <v>6856</v>
@@ -2014,7 +2014,7 @@
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A99" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B99" s="4">
         <v>6856</v>
@@ -2022,7 +2022,7 @@
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A100" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B100" s="4">
         <v>27314</v>
@@ -2030,7 +2030,7 @@
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A101" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B101" s="4">
         <v>27314</v>
@@ -2038,7 +2038,7 @@
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A102" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B102" s="4">
         <v>27314</v>
@@ -2046,7 +2046,7 @@
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A103" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B103" s="4">
         <v>4010</v>
@@ -2054,7 +2054,7 @@
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A104" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B104" s="4">
         <v>11676</v>
@@ -2062,7 +2062,7 @@
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A105" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B105" s="4">
         <v>6450</v>
@@ -2070,7 +2070,7 @@
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A106" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B106" s="4">
         <v>6450</v>
@@ -2078,7 +2078,7 @@
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A107" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B107" s="4">
         <v>2224</v>
@@ -2086,7 +2086,7 @@
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A108" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B108" s="4">
         <v>2224</v>
@@ -2094,7 +2094,7 @@
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A109" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B109" s="4">
         <v>3568</v>
@@ -2102,7 +2102,7 @@
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A110" s="8" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B110" s="4">
         <v>4010</v>
@@ -2110,7 +2110,7 @@
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A111" s="8" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B111" s="4">
         <v>27314</v>
@@ -2118,7 +2118,7 @@
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A112" s="8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B112" s="4">
         <v>6450</v>
@@ -2126,7 +2126,7 @@
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A113" s="8" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B113" s="4">
         <v>2224</v>
@@ -2134,7 +2134,7 @@
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A114" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B114" s="4">
         <v>3568</v>
@@ -2142,7 +2142,7 @@
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A115" s="8" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B115" s="4">
         <v>4010</v>
@@ -2150,7 +2150,7 @@
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A116" s="8" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B116" s="4">
         <v>4010</v>
@@ -2158,7 +2158,7 @@
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A117" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B117" s="4">
         <v>11676</v>
@@ -2166,7 +2166,7 @@
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A118" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B118" s="4">
         <v>6450</v>
@@ -2174,7 +2174,7 @@
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A119" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B119" s="4">
         <v>7000</v>
@@ -2182,7 +2182,7 @@
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A120" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B120" s="4">
         <v>7000</v>
@@ -2190,7 +2190,7 @@
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A121" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B121" s="4">
         <v>7000</v>
@@ -2198,7 +2198,7 @@
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A122" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B122" s="4">
         <v>10500</v>
@@ -2206,7 +2206,7 @@
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A123" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B123" s="4">
         <v>10500</v>
@@ -2214,7 +2214,7 @@
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A124" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B124" s="4">
         <v>10000</v>
@@ -2222,7 +2222,7 @@
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A125" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B125" s="4">
         <v>9100</v>
@@ -2230,7 +2230,7 @@
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A126" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B126" s="4">
         <v>50000</v>
@@ -2238,7 +2238,7 @@
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A127" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B127" s="4">
         <v>19395</v>
@@ -2246,7 +2246,7 @@
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A128" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B128" s="4">
         <v>71031</v>
@@ -2254,7 +2254,7 @@
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A129" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B129" s="4">
         <v>71031</v>
@@ -2262,7 +2262,7 @@
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A130" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B130" s="4">
         <v>71000</v>
@@ -2270,7 +2270,7 @@
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A131" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B131" s="4">
         <v>77779</v>
@@ -2278,7 +2278,7 @@
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A132" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B132" s="4">
         <v>48796</v>
@@ -2286,7 +2286,7 @@
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A133" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B133" s="4">
         <v>48796</v>
@@ -2294,7 +2294,7 @@
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A134" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B134" s="4">
         <v>77779</v>
@@ -2302,7 +2302,7 @@
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A135" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B135" s="4">
         <v>50000</v>
@@ -2310,7 +2310,7 @@
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A136" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B136" s="4">
         <v>92848</v>
@@ -2318,7 +2318,7 @@
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A137" s="9" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B137" s="4">
         <v>92848</v>
@@ -2326,7 +2326,7 @@
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A138" s="5" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B138" s="4">
         <v>77779</v>
@@ -2334,7 +2334,7 @@
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A139" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B139" s="4">
         <v>30000</v>
@@ -2342,7 +2342,7 @@
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A140" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B140" s="4">
         <v>30000</v>
@@ -2350,7 +2350,7 @@
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A141" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B141" s="4">
         <v>83413</v>
@@ -2358,7 +2358,7 @@
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A142" s="7" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B142" s="4">
         <v>25844</v>
@@ -2366,7 +2366,7 @@
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A143" s="7" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B143" s="4">
         <v>54000</v>
@@ -2374,7 +2374,7 @@
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A144" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B144" s="4">
         <v>69000</v>
@@ -2382,7 +2382,7 @@
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A145" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B145" s="4">
         <v>42000</v>
@@ -2390,7 +2390,7 @@
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A146" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B146" s="4">
         <v>45000</v>
@@ -2398,7 +2398,7 @@
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A147" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B147" s="4">
         <v>45000</v>
@@ -2406,7 +2406,7 @@
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A148" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B148" s="4">
         <v>37279</v>
@@ -2414,7 +2414,7 @@
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A149" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B149" s="4">
         <v>35000</v>
@@ -2422,7 +2422,7 @@
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A150" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B150" s="4">
         <v>84745</v>
@@ -2430,7 +2430,7 @@
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A151" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B151" s="4">
         <v>84745</v>
@@ -2438,7 +2438,7 @@
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A152" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B152" s="4">
         <v>7900</v>
@@ -2446,7 +2446,7 @@
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A153" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B153" s="4">
         <v>21000</v>
@@ -2454,7 +2454,7 @@
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A154" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B154" s="4">
         <v>20000</v>
@@ -2462,7 +2462,7 @@
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A155" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B155" s="4">
         <v>54112</v>
@@ -2470,7 +2470,7 @@
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A156" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B156" s="4">
         <v>21000</v>
@@ -2478,7 +2478,7 @@
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A157" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B157" s="4">
         <v>13000</v>
@@ -2486,7 +2486,7 @@
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A158" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B158" s="4">
         <v>11692</v>
@@ -2494,7 +2494,7 @@
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A159" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B159" s="4">
         <v>43548</v>
@@ -2502,7 +2502,7 @@
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A160" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B160" s="4">
         <v>80000</v>
@@ -2510,7 +2510,7 @@
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A161" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B161" s="4">
         <v>17000</v>
@@ -2518,7 +2518,7 @@
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A162" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B162" s="4">
         <v>16000</v>
@@ -2526,7 +2526,7 @@
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A163" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B163" s="4">
         <v>21000</v>
@@ -2534,7 +2534,7 @@
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A164" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B164" s="4">
         <v>20000</v>
@@ -2542,7 +2542,7 @@
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A165" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B165" s="4">
         <v>74000</v>
@@ -2550,7 +2550,7 @@
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A166" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B166" s="4">
         <v>23700</v>
@@ -2558,7 +2558,7 @@
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A167" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B167" s="4">
         <v>18000</v>
@@ -2566,7 +2566,7 @@
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A168" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B168" s="4">
         <v>59196</v>
@@ -2574,7 +2574,7 @@
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A169" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B169" s="4">
         <v>4032</v>
@@ -2582,7 +2582,7 @@
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A170" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B170" s="4">
         <v>4632</v>
@@ -2590,7 +2590,7 @@
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A171" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B171" s="4">
         <v>4032</v>
@@ -2598,7 +2598,7 @@
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A172" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B172" s="4">
         <v>23942</v>
@@ -2606,7 +2606,7 @@
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A173" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B173" s="4">
         <v>10000</v>
@@ -2614,7 +2614,7 @@
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A174" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B174" s="4">
         <v>5660</v>
@@ -2622,7 +2622,7 @@
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A175" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B175" s="4">
         <v>5660</v>
@@ -2630,7 +2630,7 @@
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A176" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B176" s="4">
         <v>5560</v>
@@ -2638,7 +2638,7 @@
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A177" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B177" s="4">
         <v>6200</v>
@@ -2646,7 +2646,7 @@
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A178" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B178" s="4">
         <v>6200</v>
@@ -2654,7 +2654,7 @@
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A179" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B179" s="4">
         <v>5560</v>
@@ -2662,7 +2662,7 @@
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A180" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B180" s="4">
         <v>5384</v>
@@ -2670,7 +2670,7 @@
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A181" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B181" s="10">
         <v>230394</v>
@@ -2678,7 +2678,7 @@
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A182" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B182" s="10">
         <v>18000</v>
@@ -2686,7 +2686,7 @@
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A183" s="8" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B183" s="10">
         <v>18000</v>
@@ -2694,7 +2694,7 @@
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A184" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B184" s="4">
         <v>54704</v>
@@ -2702,7 +2702,7 @@
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A185" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B185" s="4">
         <v>21000</v>
@@ -2710,7 +2710,7 @@
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A186" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B186" s="4">
         <v>20000</v>
@@ -2718,7 +2718,7 @@
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A187" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B187" s="4">
         <v>80000</v>
@@ -2726,7 +2726,7 @@
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A188" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B188" s="4">
         <v>50000</v>
@@ -2734,7 +2734,7 @@
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A189" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B189" s="4">
         <v>74000</v>
@@ -2742,7 +2742,7 @@
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A190" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B190" s="4">
         <v>5500</v>

--- a/grossdie.xlsx
+++ b/grossdie.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wenqiang.ding\Desktop\0401\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wenqiang.ding\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9FD0AA5-8F87-4B64-8875-3C99ECF88BDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1CBA38E-230F-4815-A510-46A2354C1CAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,6 +27,10 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="191">
   <si>
+    <t>品名</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>GROSS DIE</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -774,10 +778,6 @@
   </si>
   <si>
     <t>ZH6342A</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>晶圆</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1230,15 +1230,15 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>190</v>
+        <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B2" s="4">
         <v>11463</v>
@@ -1246,7 +1246,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B3" s="4">
         <v>11463</v>
@@ -1254,7 +1254,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B4" s="4">
         <v>11463</v>
@@ -1262,7 +1262,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B5" s="4">
         <v>11463</v>
@@ -1270,7 +1270,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B6" s="4">
         <v>11463</v>
@@ -1278,7 +1278,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B7" s="4">
         <v>11463</v>
@@ -1286,7 +1286,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B8" s="4">
         <v>37000</v>
@@ -1294,7 +1294,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B9" s="4">
         <v>7700</v>
@@ -1302,7 +1302,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B10" s="4">
         <v>7700</v>
@@ -1310,7 +1310,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B11" s="4">
         <v>7700</v>
@@ -1318,7 +1318,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B12" s="4">
         <v>5665</v>
@@ -1326,7 +1326,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B13" s="4">
         <v>28507</v>
@@ -1334,7 +1334,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B14" s="4">
         <v>28507</v>
@@ -1342,7 +1342,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B15" s="4">
         <v>28507</v>
@@ -1350,7 +1350,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B16" s="4">
         <v>28507</v>
@@ -1358,7 +1358,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B17" s="4">
         <v>28507</v>
@@ -1366,7 +1366,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B18" s="4">
         <v>19900</v>
@@ -1374,7 +1374,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B19" s="4">
         <v>19900</v>
@@ -1382,7 +1382,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B20" s="4">
         <v>24053</v>
@@ -1390,7 +1390,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B21" s="4">
         <v>24053</v>
@@ -1398,7 +1398,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B22" s="4">
         <v>24053</v>
@@ -1406,7 +1406,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B23" s="4">
         <v>16204</v>
@@ -1414,7 +1414,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B24" s="4">
         <v>16204</v>
@@ -1422,7 +1422,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B25" s="4">
         <v>16204</v>
@@ -1430,7 +1430,7 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B26" s="4">
         <v>16204</v>
@@ -1438,7 +1438,7 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B27" s="4">
         <v>16204</v>
@@ -1446,7 +1446,7 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B28" s="4">
         <v>16204</v>
@@ -1454,7 +1454,7 @@
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B29" s="4">
         <v>16204</v>
@@ -1462,7 +1462,7 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B30" s="4">
         <v>16204</v>
@@ -1470,7 +1470,7 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B31" s="4">
         <v>16204</v>
@@ -1478,7 +1478,7 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B32" s="4">
         <v>9000</v>
@@ -1486,7 +1486,7 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B33" s="4">
         <v>7854</v>
@@ -1494,7 +1494,7 @@
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B34" s="4">
         <v>3233</v>
@@ -1502,7 +1502,7 @@
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B35" s="4">
         <v>3233</v>
@@ -1510,7 +1510,7 @@
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B36" s="4">
         <v>3233</v>
@@ -1518,7 +1518,7 @@
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A37" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B37" s="4">
         <v>4000</v>
@@ -1526,7 +1526,7 @@
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B38" s="4">
         <v>4000</v>
@@ -1534,7 +1534,7 @@
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A39" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B39" s="4">
         <v>13888</v>
@@ -1542,7 +1542,7 @@
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B40" s="4">
         <v>14500</v>
@@ -1550,7 +1550,7 @@
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A41" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B41" s="4">
         <v>24053</v>
@@ -1558,7 +1558,7 @@
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A42" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B42" s="4">
         <v>24053</v>
@@ -1566,7 +1566,7 @@
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A43" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B43" s="4">
         <v>4250</v>
@@ -1574,7 +1574,7 @@
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A44" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B44" s="4">
         <v>4250</v>
@@ -1582,7 +1582,7 @@
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A45" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B45" s="4">
         <v>6942</v>
@@ -1590,7 +1590,7 @@
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A46" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B46" s="4">
         <v>16204</v>
@@ -1598,7 +1598,7 @@
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A47" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B47" s="4">
         <v>16204</v>
@@ -1606,7 +1606,7 @@
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A48" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B48" s="4">
         <v>16204</v>
@@ -1614,7 +1614,7 @@
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A49" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B49" s="4">
         <v>3947</v>
@@ -1622,7 +1622,7 @@
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A50" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B50" s="4">
         <v>38147</v>
@@ -1630,7 +1630,7 @@
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A51" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B51" s="4">
         <v>38147</v>
@@ -1638,7 +1638,7 @@
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A52" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B52" s="4">
         <v>38147</v>
@@ -1646,7 +1646,7 @@
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A53" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B53" s="4">
         <v>38147</v>
@@ -1654,7 +1654,7 @@
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A54" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B54" s="4">
         <v>20915</v>
@@ -1662,7 +1662,7 @@
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A55" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B55" s="4">
         <v>20920</v>
@@ -1670,7 +1670,7 @@
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A56" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B56" s="4">
         <v>27000</v>
@@ -1678,7 +1678,7 @@
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A57" s="5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B57" s="4">
         <v>16194</v>
@@ -1686,7 +1686,7 @@
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A58" s="5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B58" s="4">
         <v>16194</v>
@@ -1694,7 +1694,7 @@
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A59" s="5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B59" s="4">
         <v>16194</v>
@@ -1702,7 +1702,7 @@
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A60" s="5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B60" s="4">
         <v>16194</v>
@@ -1710,7 +1710,7 @@
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A61" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B61" s="4">
         <v>16194</v>
@@ -1718,7 +1718,7 @@
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A62" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B62" s="4">
         <v>16194</v>
@@ -1726,7 +1726,7 @@
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A63" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B63" s="4">
         <v>20920</v>
@@ -1734,7 +1734,7 @@
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A64" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B64" s="4">
         <v>11249</v>
@@ -1742,7 +1742,7 @@
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A65" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B65" s="4">
         <v>11249</v>
@@ -1750,7 +1750,7 @@
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A66" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B66" s="4">
         <v>18810</v>
@@ -1758,7 +1758,7 @@
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A67" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B67" s="4">
         <v>28507</v>
@@ -1766,7 +1766,7 @@
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A68" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B68" s="4">
         <v>28507</v>
@@ -1774,7 +1774,7 @@
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A69" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B69" s="4">
         <v>28507</v>
@@ -1782,7 +1782,7 @@
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A70" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B70" s="4">
         <v>28507</v>
@@ -1790,7 +1790,7 @@
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A71" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B71" s="4">
         <v>28507</v>
@@ -1798,7 +1798,7 @@
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A72" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B72" s="4">
         <v>18326</v>
@@ -1806,7 +1806,7 @@
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A73" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B73" s="4">
         <v>15391</v>
@@ -1814,7 +1814,7 @@
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A74" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B74" s="4">
         <v>7368</v>
@@ -1822,7 +1822,7 @@
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A75" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B75" s="4">
         <v>8134</v>
@@ -1830,7 +1830,7 @@
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A76" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B76" s="4">
         <v>8134</v>
@@ -1838,7 +1838,7 @@
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A77" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B77" s="4">
         <v>8134</v>
@@ -1846,7 +1846,7 @@
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A78" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B78" s="4">
         <v>7090</v>
@@ -1854,7 +1854,7 @@
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A79" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B79" s="4">
         <v>7090</v>
@@ -1862,7 +1862,7 @@
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A80" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B80" s="4">
         <v>7368</v>
@@ -1870,7 +1870,7 @@
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A81" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B81" s="4">
         <v>3308</v>
@@ -1878,7 +1878,7 @@
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A82" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B82" s="4">
         <v>4278</v>
@@ -1886,7 +1886,7 @@
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A83" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B83" s="4">
         <v>1833</v>
@@ -1894,7 +1894,7 @@
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A84" s="5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B84" s="4">
         <v>1833</v>
@@ -1902,7 +1902,7 @@
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A85" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B85" s="4">
         <v>6308</v>
@@ -1910,7 +1910,7 @@
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A86" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B86" s="4">
         <v>6100</v>
@@ -1918,7 +1918,7 @@
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A87" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B87" s="4">
         <v>28400</v>
@@ -1926,7 +1926,7 @@
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A88" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B88" s="4">
         <v>28400</v>
@@ -1934,7 +1934,7 @@
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A89" s="7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B89" s="4">
         <v>2214</v>
@@ -1942,7 +1942,7 @@
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A90" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B90" s="4">
         <v>45000</v>
@@ -1950,7 +1950,7 @@
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A91" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B91" s="4">
         <v>43500</v>
@@ -1958,7 +1958,7 @@
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A92" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B92" s="4">
         <v>45000</v>
@@ -1966,7 +1966,7 @@
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A93" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B93" s="4">
         <v>45000</v>
@@ -1974,7 +1974,7 @@
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A94" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B94" s="4">
         <v>43548</v>
@@ -1982,7 +1982,7 @@
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A95" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B95" s="4">
         <v>26000</v>
@@ -1990,7 +1990,7 @@
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A96" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B96" s="4">
         <v>10000</v>
@@ -1998,7 +1998,7 @@
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A97" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B97" s="4">
         <v>27314</v>
@@ -2006,7 +2006,7 @@
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A98" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B98" s="4">
         <v>6856</v>
@@ -2014,7 +2014,7 @@
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A99" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B99" s="4">
         <v>6856</v>
@@ -2022,7 +2022,7 @@
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A100" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B100" s="4">
         <v>27314</v>
@@ -2030,7 +2030,7 @@
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A101" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B101" s="4">
         <v>27314</v>
@@ -2038,7 +2038,7 @@
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A102" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B102" s="4">
         <v>27314</v>
@@ -2046,7 +2046,7 @@
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A103" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B103" s="4">
         <v>4010</v>
@@ -2054,7 +2054,7 @@
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A104" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B104" s="4">
         <v>11676</v>
@@ -2062,7 +2062,7 @@
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A105" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B105" s="4">
         <v>6450</v>
@@ -2070,7 +2070,7 @@
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A106" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B106" s="4">
         <v>6450</v>
@@ -2078,7 +2078,7 @@
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A107" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B107" s="4">
         <v>2224</v>
@@ -2086,7 +2086,7 @@
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A108" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B108" s="4">
         <v>2224</v>
@@ -2094,7 +2094,7 @@
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A109" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B109" s="4">
         <v>3568</v>
@@ -2102,7 +2102,7 @@
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A110" s="8" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B110" s="4">
         <v>4010</v>
@@ -2110,7 +2110,7 @@
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A111" s="8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B111" s="4">
         <v>27314</v>
@@ -2118,7 +2118,7 @@
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A112" s="8" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B112" s="4">
         <v>6450</v>
@@ -2126,7 +2126,7 @@
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A113" s="8" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B113" s="4">
         <v>2224</v>
@@ -2134,7 +2134,7 @@
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A114" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B114" s="4">
         <v>3568</v>
@@ -2142,7 +2142,7 @@
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A115" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B115" s="4">
         <v>4010</v>
@@ -2150,7 +2150,7 @@
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A116" s="8" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B116" s="4">
         <v>4010</v>
@@ -2158,7 +2158,7 @@
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A117" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B117" s="4">
         <v>11676</v>
@@ -2166,7 +2166,7 @@
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A118" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B118" s="4">
         <v>6450</v>
@@ -2174,7 +2174,7 @@
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A119" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B119" s="4">
         <v>7000</v>
@@ -2182,7 +2182,7 @@
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A120" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B120" s="4">
         <v>7000</v>
@@ -2190,7 +2190,7 @@
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A121" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B121" s="4">
         <v>7000</v>
@@ -2198,7 +2198,7 @@
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A122" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B122" s="4">
         <v>10500</v>
@@ -2206,7 +2206,7 @@
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A123" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B123" s="4">
         <v>10500</v>
@@ -2214,7 +2214,7 @@
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A124" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B124" s="4">
         <v>10000</v>
@@ -2222,7 +2222,7 @@
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A125" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B125" s="4">
         <v>9100</v>
@@ -2230,7 +2230,7 @@
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A126" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B126" s="4">
         <v>50000</v>
@@ -2238,7 +2238,7 @@
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A127" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B127" s="4">
         <v>19395</v>
@@ -2246,7 +2246,7 @@
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A128" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B128" s="4">
         <v>71031</v>
@@ -2254,7 +2254,7 @@
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A129" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B129" s="4">
         <v>71031</v>
@@ -2262,7 +2262,7 @@
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A130" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B130" s="4">
         <v>71000</v>
@@ -2270,7 +2270,7 @@
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A131" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B131" s="4">
         <v>77779</v>
@@ -2278,7 +2278,7 @@
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A132" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B132" s="4">
         <v>48796</v>
@@ -2286,7 +2286,7 @@
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A133" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B133" s="4">
         <v>48796</v>
@@ -2294,7 +2294,7 @@
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A134" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B134" s="4">
         <v>77779</v>
@@ -2302,7 +2302,7 @@
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A135" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B135" s="4">
         <v>50000</v>
@@ -2310,7 +2310,7 @@
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A136" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B136" s="4">
         <v>92848</v>
@@ -2318,7 +2318,7 @@
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A137" s="9" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B137" s="4">
         <v>92848</v>
@@ -2326,7 +2326,7 @@
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A138" s="5" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B138" s="4">
         <v>77779</v>
@@ -2334,7 +2334,7 @@
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A139" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B139" s="4">
         <v>30000</v>
@@ -2342,7 +2342,7 @@
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A140" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B140" s="4">
         <v>30000</v>
@@ -2350,7 +2350,7 @@
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A141" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B141" s="4">
         <v>83413</v>
@@ -2358,7 +2358,7 @@
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A142" s="7" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B142" s="4">
         <v>25844</v>
@@ -2366,7 +2366,7 @@
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A143" s="7" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B143" s="4">
         <v>54000</v>
@@ -2374,7 +2374,7 @@
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A144" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B144" s="4">
         <v>69000</v>
@@ -2382,7 +2382,7 @@
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A145" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B145" s="4">
         <v>42000</v>
@@ -2390,7 +2390,7 @@
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A146" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B146" s="4">
         <v>45000</v>
@@ -2398,7 +2398,7 @@
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A147" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B147" s="4">
         <v>45000</v>
@@ -2406,7 +2406,7 @@
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A148" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B148" s="4">
         <v>37279</v>
@@ -2414,7 +2414,7 @@
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A149" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B149" s="4">
         <v>35000</v>
@@ -2422,7 +2422,7 @@
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A150" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B150" s="4">
         <v>84745</v>
@@ -2430,7 +2430,7 @@
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A151" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B151" s="4">
         <v>84745</v>
@@ -2438,7 +2438,7 @@
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A152" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B152" s="4">
         <v>7900</v>
@@ -2446,7 +2446,7 @@
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A153" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B153" s="4">
         <v>21000</v>
@@ -2454,7 +2454,7 @@
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A154" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B154" s="4">
         <v>20000</v>
@@ -2462,7 +2462,7 @@
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A155" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B155" s="4">
         <v>54112</v>
@@ -2470,7 +2470,7 @@
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A156" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B156" s="4">
         <v>21000</v>
@@ -2478,7 +2478,7 @@
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A157" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B157" s="4">
         <v>13000</v>
@@ -2486,7 +2486,7 @@
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A158" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B158" s="4">
         <v>11692</v>
@@ -2494,7 +2494,7 @@
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A159" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B159" s="4">
         <v>43548</v>
@@ -2502,7 +2502,7 @@
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A160" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B160" s="4">
         <v>80000</v>
@@ -2510,7 +2510,7 @@
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A161" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B161" s="4">
         <v>17000</v>
@@ -2518,7 +2518,7 @@
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A162" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B162" s="4">
         <v>16000</v>
@@ -2526,7 +2526,7 @@
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A163" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B163" s="4">
         <v>21000</v>
@@ -2534,7 +2534,7 @@
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A164" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B164" s="4">
         <v>20000</v>
@@ -2542,7 +2542,7 @@
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A165" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B165" s="4">
         <v>74000</v>
@@ -2550,7 +2550,7 @@
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A166" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B166" s="4">
         <v>23700</v>
@@ -2558,7 +2558,7 @@
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A167" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B167" s="4">
         <v>18000</v>
@@ -2566,7 +2566,7 @@
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A168" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B168" s="4">
         <v>59196</v>
@@ -2574,7 +2574,7 @@
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A169" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B169" s="4">
         <v>4032</v>
@@ -2582,7 +2582,7 @@
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A170" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B170" s="4">
         <v>4632</v>
@@ -2590,7 +2590,7 @@
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A171" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B171" s="4">
         <v>4032</v>
@@ -2598,7 +2598,7 @@
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A172" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B172" s="4">
         <v>23942</v>
@@ -2606,7 +2606,7 @@
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A173" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B173" s="4">
         <v>10000</v>
@@ -2614,7 +2614,7 @@
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A174" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B174" s="4">
         <v>5660</v>
@@ -2622,7 +2622,7 @@
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A175" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B175" s="4">
         <v>5660</v>
@@ -2630,7 +2630,7 @@
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A176" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B176" s="4">
         <v>5560</v>
@@ -2638,7 +2638,7 @@
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A177" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B177" s="4">
         <v>6200</v>
@@ -2646,7 +2646,7 @@
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A178" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B178" s="4">
         <v>6200</v>
@@ -2654,7 +2654,7 @@
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A179" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B179" s="4">
         <v>5560</v>
@@ -2662,7 +2662,7 @@
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A180" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B180" s="4">
         <v>5384</v>
@@ -2670,7 +2670,7 @@
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A181" s="8" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B181" s="10">
         <v>230394</v>
@@ -2678,7 +2678,7 @@
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A182" s="8" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B182" s="10">
         <v>18000</v>
@@ -2686,7 +2686,7 @@
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A183" s="8" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B183" s="10">
         <v>18000</v>
@@ -2694,7 +2694,7 @@
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A184" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B184" s="4">
         <v>54704</v>
@@ -2702,7 +2702,7 @@
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A185" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B185" s="4">
         <v>21000</v>
@@ -2710,7 +2710,7 @@
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A186" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B186" s="4">
         <v>20000</v>
@@ -2718,7 +2718,7 @@
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A187" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B187" s="4">
         <v>80000</v>
@@ -2726,7 +2726,7 @@
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A188" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B188" s="4">
         <v>50000</v>
@@ -2734,7 +2734,7 @@
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A189" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B189" s="4">
         <v>74000</v>
@@ -2742,7 +2742,7 @@
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A190" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B190" s="4">
         <v>5500</v>
